--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N46_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.26582534155514</v>
+        <v>5.89319661800271</v>
       </c>
       <c r="D2" t="n">
-        <v>21.68768317430975</v>
+        <v>3.524248515825334</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
